--- a/Result/profitability/8092.xlsx
+++ b/Result/profitability/8092.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.28</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.1125</v>
+        <v>-0.11625</v>
       </c>
       <c r="N2" t="n">
-        <v>12.315</v>
+        <v>11.5425</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.13</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.1325</v>
+        <v>-0.08625000000000002</v>
       </c>
       <c r="N3" t="n">
-        <v>10.70125</v>
+        <v>12.04</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.08625000000000002</v>
+        <v>-0.04250000000000002</v>
       </c>
       <c r="N4" t="n">
-        <v>10.70375</v>
+        <v>13.66125</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>-0.57</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.11375</v>
+        <v>-0.10375</v>
       </c>
       <c r="N5" t="n">
-        <v>11.31125</v>
+        <v>10.9725</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1139,10 +1139,10 @@
         <v>-0.27</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.1375</v>
+        <v>-0.16375</v>
       </c>
       <c r="N6" t="n">
-        <v>8.76375</v>
+        <v>8.475</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1266,10 +1266,10 @@
         <v>-0.41</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.215</v>
+        <v>-0.2425</v>
       </c>
       <c r="N7" t="n">
-        <v>6.67375</v>
+        <v>8.06875</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1393,10 +1393,10 @@
         <v>-0.12</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.2575</v>
+        <v>-0.2225</v>
       </c>
       <c r="N8" t="n">
-        <v>6.92625</v>
+        <v>8.53875</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -2030,7 +2030,7 @@
         <v>-0.09</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.08750000000000001</v>
+        <v>-0.08750000000000002</v>
       </c>
       <c r="N13" t="n">
         <v>12.04</v>
@@ -9838,6 +9838,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>8092</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>90</v>
+      </c>
+      <c r="D75" t="n">
+        <v>72</v>
+      </c>
+      <c r="E75" t="n">
+        <v>18</v>
+      </c>
+      <c r="F75" t="n">
+        <v>19.46</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-2</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-2.19%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>2</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-0</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-0</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.07750000000000001</v>
+      </c>
+      <c r="N75" t="n">
+        <v>13.55625</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>1.966463414634147</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-2.710000000000001</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.1222372575552548</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
